--- a/docs/baselines/august-2026-export-baseline.xlsx
+++ b/docs/baselines/august-2026-export-baseline.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3826">
   <si>
     <t>MOKA</t>
   </si>
@@ -9735,6 +9735,9 @@
   </si>
   <si>
     <t>Liat Leng</t>
+  </si>
+  <si>
+    <t>Day use (hourly): company revenue, not on the owner's calendar | Auto-assigned from EZEE room J-28-06 (Rental Unit) | moved from Ekocheras J-28-06 7 Sep per ground rule 22</t>
   </si>
   <si>
     <t>RES31093</t>
@@ -64930,7 +64933,7 @@
         <v>3239</v>
       </c>
       <c r="F902" t="s">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="G902" t="s">
         <v>317</v>
@@ -64960,16 +64963,16 @@
         <v>0.0</v>
       </c>
       <c r="P902">
-        <v>0.0</v>
+        <v>2.22</v>
       </c>
       <c r="Q902" t="s">
         <v>3238</v>
       </c>
       <c r="R902">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="S902" t="s">
-        <v>3236</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="903" spans="1:19">
@@ -64977,10 +64980,10 @@
         <v>67832</v>
       </c>
       <c r="B903" t="s">
-        <v>3240</v>
+        <v>3241</v>
       </c>
       <c r="C903" t="s">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="D903" t="s">
         <v>222</v>
@@ -65022,7 +65025,7 @@
         <v>42.24</v>
       </c>
       <c r="Q903" t="s">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="R903">
         <v>615.6</v>
@@ -65036,10 +65039,10 @@
         <v>67833</v>
       </c>
       <c r="B904" t="s">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="C904" t="s">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="D904" t="s">
         <v>3121</v>
@@ -65081,7 +65084,7 @@
         <v>15.2</v>
       </c>
       <c r="Q904" t="s">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="R904">
         <v>205.2</v>
@@ -65095,16 +65098,16 @@
         <v>67834</v>
       </c>
       <c r="B905" t="s">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="C905" t="s">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="D905" t="s">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="E905" t="s">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="F905" t="s">
         <v>621</v>
@@ -65140,7 +65143,7 @@
         <v>8.64</v>
       </c>
       <c r="Q905" t="s">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="R905">
         <v>162.0</v>
@@ -65154,16 +65157,16 @@
         <v>67835</v>
       </c>
       <c r="B906" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C906" t="s">
+        <v>3250</v>
+      </c>
+      <c r="D906" t="s">
+        <v>3247</v>
+      </c>
+      <c r="E906" t="s">
         <v>3248</v>
-      </c>
-      <c r="C906" t="s">
-        <v>3249</v>
-      </c>
-      <c r="D906" t="s">
-        <v>3246</v>
-      </c>
-      <c r="E906" t="s">
-        <v>3247</v>
       </c>
       <c r="F906" t="s">
         <v>473</v>
@@ -65199,7 +65202,7 @@
         <v>8.64</v>
       </c>
       <c r="Q906" t="s">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="R906">
         <v>162.0</v>
@@ -65213,16 +65216,16 @@
         <v>67836</v>
       </c>
       <c r="B907" t="s">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="C907" t="s">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="D907" t="s">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="E907" t="s">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="F907" t="s">
         <v>684</v>
@@ -65258,7 +65261,7 @@
         <v>3.98</v>
       </c>
       <c r="Q907" t="s">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="R907">
         <v>99.0</v>
@@ -65272,16 +65275,16 @@
         <v>67837</v>
       </c>
       <c r="B908" t="s">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="C908" t="s">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="D908" t="s">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="E908" t="s">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="F908" t="s">
         <v>669</v>
@@ -65317,7 +65320,7 @@
         <v>24.73</v>
       </c>
       <c r="Q908" t="s">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="R908">
         <v>377.92</v>
@@ -65331,16 +65334,16 @@
         <v>67838</v>
       </c>
       <c r="B909" t="s">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="C909" t="s">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="D909" t="s">
-        <v>3260</v>
+        <v>3261</v>
       </c>
       <c r="E909" t="s">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="F909" t="s">
         <v>519</v>
@@ -65376,13 +65379,13 @@
         <v>6.94</v>
       </c>
       <c r="Q909" t="s">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="R909">
         <v>138.98</v>
       </c>
       <c r="S909" t="s">
-        <v>3262</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="910" spans="1:19">
@@ -65390,16 +65393,16 @@
         <v>67839</v>
       </c>
       <c r="B910" t="s">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="C910" t="s">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="D910" t="s">
         <v>603</v>
       </c>
       <c r="E910" t="s">
-        <v>3265</v>
+        <v>3266</v>
       </c>
       <c r="F910" t="s">
         <v>523</v>
@@ -65435,7 +65438,7 @@
         <v>29.35</v>
       </c>
       <c r="Q910" t="s">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="R910">
         <v>441.54</v>
@@ -65449,16 +65452,16 @@
         <v>67840</v>
       </c>
       <c r="B911" t="s">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="C911" t="s">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="D911" t="s">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="E911" t="s">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="F911" t="s">
         <v>504</v>
@@ -65494,7 +65497,7 @@
         <v>21.65</v>
       </c>
       <c r="Q911" t="s">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="R911">
         <v>337.57</v>
@@ -65508,16 +65511,16 @@
         <v>67841</v>
       </c>
       <c r="B912" t="s">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="C912" t="s">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="D912" t="s">
         <v>527</v>
       </c>
       <c r="E912" t="s">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="F912" t="s">
         <v>392</v>
@@ -65553,7 +65556,7 @@
         <v>17.63</v>
       </c>
       <c r="Q912" t="s">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="R912">
         <v>275.62</v>
@@ -65567,10 +65570,10 @@
         <v>67842</v>
       </c>
       <c r="B913" t="s">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="C913" t="s">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="D913" t="s">
         <v>657</v>
@@ -65612,7 +65615,7 @@
         <v>11.84</v>
       </c>
       <c r="Q913" t="s">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="R913">
         <v>205.2</v>
@@ -65626,13 +65629,13 @@
         <v>67843</v>
       </c>
       <c r="B914" t="s">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="C914" t="s">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="D914" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="E914" t="s">
         <v>594</v>
@@ -65671,7 +65674,7 @@
         <v>5.91</v>
       </c>
       <c r="Q914" t="s">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="R914">
         <v>125.23</v>
@@ -65685,13 +65688,13 @@
         <v>67844</v>
       </c>
       <c r="B915" t="s">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="C915" t="s">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="D915" t="s">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="E915" t="s">
         <v>942</v>
@@ -65730,7 +65733,7 @@
         <v>24.08</v>
       </c>
       <c r="Q915" t="s">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="R915">
         <v>370.44</v>
@@ -65744,16 +65747,16 @@
         <v>67845</v>
       </c>
       <c r="B916" t="s">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="C916" t="s">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="D916" t="s">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="E916" t="s">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="F916" t="s">
         <v>664</v>
@@ -65789,7 +65792,7 @@
         <v>22.6</v>
       </c>
       <c r="Q916" t="s">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="R916">
         <v>350.4</v>
@@ -65803,10 +65806,10 @@
         <v>67846</v>
       </c>
       <c r="B917" t="s">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="C917" t="s">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="D917" t="s">
         <v>386</v>
@@ -65848,7 +65851,7 @@
         <v>16.65</v>
       </c>
       <c r="Q917" t="s">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="R917">
         <v>270.89</v>
@@ -65862,10 +65865,10 @@
         <v>67847</v>
       </c>
       <c r="B918" t="s">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="C918" t="s">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="D918" t="s">
         <v>2322</v>
@@ -65907,13 +65910,13 @@
         <v>20.45</v>
       </c>
       <c r="Q918" t="s">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="R918">
         <v>321.33</v>
       </c>
       <c r="S918" t="s">
-        <v>3289</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="919" spans="1:19">
@@ -65921,13 +65924,13 @@
         <v>67848</v>
       </c>
       <c r="B919" t="s">
-        <v>3290</v>
+        <v>3291</v>
       </c>
       <c r="C919" t="s">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="D919" t="s">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="E919" t="s">
         <v>2901</v>
@@ -65966,7 +65969,7 @@
         <v>8.57</v>
       </c>
       <c r="Q919" t="s">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="R919">
         <v>159.73</v>
@@ -65980,16 +65983,16 @@
         <v>67849</v>
       </c>
       <c r="B920" t="s">
-        <v>3293</v>
+        <v>3294</v>
       </c>
       <c r="C920" t="s">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="D920" t="s">
-        <v>3295</v>
+        <v>3296</v>
       </c>
       <c r="E920" t="s">
-        <v>3296</v>
+        <v>3297</v>
       </c>
       <c r="F920" t="s">
         <v>408</v>
@@ -66025,7 +66028,7 @@
         <v>19.91</v>
       </c>
       <c r="Q920" t="s">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="R920">
         <v>314.05</v>
@@ -66039,10 +66042,10 @@
         <v>67850</v>
       </c>
       <c r="B921" t="s">
-        <v>3297</v>
+        <v>3298</v>
       </c>
       <c r="C921" t="s">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="D921" t="s">
         <v>663</v>
@@ -66084,7 +66087,7 @@
         <v>5.56</v>
       </c>
       <c r="Q921" t="s">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="R921">
         <v>120.28</v>
@@ -66098,16 +66101,16 @@
         <v>67851</v>
       </c>
       <c r="B922" t="s">
-        <v>3299</v>
+        <v>3300</v>
       </c>
       <c r="C922" t="s">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="D922" t="s">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="E922" t="s">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="F922" t="s">
         <v>612</v>
@@ -66143,7 +66146,7 @@
         <v>27.08</v>
       </c>
       <c r="Q922" t="s">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="R922">
         <v>410.86</v>
@@ -66157,13 +66160,13 @@
         <v>67852</v>
       </c>
       <c r="B923" t="s">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="C923" t="s">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="D923" t="s">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="E923" t="s">
         <v>1627</v>
@@ -66202,7 +66205,7 @@
         <v>12.03</v>
       </c>
       <c r="Q923" t="s">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="R923">
         <v>207.71</v>
@@ -66216,16 +66219,16 @@
         <v>67853</v>
       </c>
       <c r="B924" t="s">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="C924" t="s">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="D924" t="s">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="E924" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="F924" t="s">
         <v>246</v>
@@ -66261,7 +66264,7 @@
         <v>61.82</v>
       </c>
       <c r="Q924" t="s">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="R924">
         <v>890.62</v>
@@ -66281,7 +66284,7 @@
         <v>2031</v>
       </c>
       <c r="D925" t="s">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="E925" t="s">
         <v>2870</v>
@@ -66334,16 +66337,16 @@
         <v>67855</v>
       </c>
       <c r="B926" t="s">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="C926" t="s">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="D926" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="E926" t="s">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="F926" t="s">
         <v>376</v>
@@ -66379,7 +66382,7 @@
         <v>15.19</v>
       </c>
       <c r="Q926" t="s">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="R926">
         <v>261.11</v>
@@ -66393,16 +66396,16 @@
         <v>67856</v>
       </c>
       <c r="B927" t="s">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="C927" t="s">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="D927" t="s">
         <v>2698</v>
       </c>
       <c r="E927" t="s">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="F927" t="s">
         <v>439</v>
@@ -66438,7 +66441,7 @@
         <v>36.65</v>
       </c>
       <c r="Q927" t="s">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="R927">
         <v>540.0</v>
@@ -66452,10 +66455,10 @@
         <v>67857</v>
       </c>
       <c r="B928" t="s">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="C928" t="s">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="D928" t="s">
         <v>279</v>
@@ -66497,7 +66500,7 @@
         <v>27.2</v>
       </c>
       <c r="Q928" t="s">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="R928">
         <v>367.2</v>
@@ -66511,16 +66514,16 @@
         <v>67858</v>
       </c>
       <c r="B929" t="s">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="C929" t="s">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="D929" t="s">
         <v>1165</v>
       </c>
       <c r="E929" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="F929" t="s">
         <v>24</v>
@@ -66556,7 +66559,7 @@
         <v>41.73</v>
       </c>
       <c r="Q929" t="s">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="R929">
         <v>619.37</v>
@@ -66570,10 +66573,10 @@
         <v>67859</v>
       </c>
       <c r="B930" t="s">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="C930" t="s">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="D930" t="s">
         <v>370</v>
@@ -66615,7 +66618,7 @@
         <v>8.8</v>
       </c>
       <c r="Q930" t="s">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="R930">
         <v>118.8</v>
@@ -66629,16 +66632,16 @@
         <v>67860</v>
       </c>
       <c r="B931" t="s">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="C931" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="D931" t="s">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="E931" t="s">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="F931" t="s">
         <v>580</v>
@@ -66674,7 +66677,7 @@
         <v>14.26</v>
       </c>
       <c r="Q931" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="R931">
         <v>256.4</v>
@@ -66688,10 +66691,10 @@
         <v>67861</v>
       </c>
       <c r="B932" t="s">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="C932" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="D932" t="s">
         <v>888</v>
@@ -66733,7 +66736,7 @@
         <v>5.55</v>
       </c>
       <c r="Q932" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="R932">
         <v>120.14</v>
@@ -66747,16 +66750,16 @@
         <v>67862</v>
       </c>
       <c r="B933" t="s">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="C933" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="D933" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="E933" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="F933" t="s">
         <v>343</v>
@@ -66792,7 +66795,7 @@
         <v>9.99</v>
       </c>
       <c r="Q933" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="R933">
         <v>180.09</v>
@@ -66806,16 +66809,16 @@
         <v>67863</v>
       </c>
       <c r="B934" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="C934" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="D934" t="s">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="E934" t="s">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="F934" t="s">
         <v>444</v>
@@ -66851,7 +66854,7 @@
         <v>23.23</v>
       </c>
       <c r="Q934" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="R934">
         <v>358.83</v>
@@ -66865,13 +66868,13 @@
         <v>67864</v>
       </c>
       <c r="B935" t="s">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="C935" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="D935" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="E935" t="s">
         <v>2027</v>
@@ -66910,13 +66913,13 @@
         <v>33.08</v>
       </c>
       <c r="Q935" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="R935">
         <v>491.8</v>
       </c>
       <c r="S935" t="s">
-        <v>3342</v>
+        <v>3343</v>
       </c>
     </row>
     <row r="936" spans="1:19">
@@ -66924,16 +66927,16 @@
         <v>67865</v>
       </c>
       <c r="B936" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="C936" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="D936" t="s">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="E936" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="F936" t="s">
         <v>354</v>
@@ -66969,7 +66972,7 @@
         <v>6.39</v>
       </c>
       <c r="Q936" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="R936">
         <v>131.53</v>
@@ -66983,16 +66986,16 @@
         <v>67866</v>
       </c>
       <c r="B937" t="s">
+        <v>3348</v>
+      </c>
+      <c r="C937" t="s">
+        <v>3349</v>
+      </c>
+      <c r="D937" t="s">
+        <v>3346</v>
+      </c>
+      <c r="E937" t="s">
         <v>3347</v>
-      </c>
-      <c r="C937" t="s">
-        <v>3348</v>
-      </c>
-      <c r="D937" t="s">
-        <v>3345</v>
-      </c>
-      <c r="E937" t="s">
-        <v>3346</v>
       </c>
       <c r="F937" t="s">
         <v>566</v>
@@ -67028,7 +67031,7 @@
         <v>12.08</v>
       </c>
       <c r="Q937" t="s">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="R937">
         <v>208.28</v>
@@ -67042,16 +67045,16 @@
         <v>67867</v>
       </c>
       <c r="B938" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="C938" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="D938" t="s">
         <v>1512</v>
       </c>
       <c r="E938" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="F938" t="s">
         <v>333</v>
@@ -67087,13 +67090,13 @@
         <v>4.54</v>
       </c>
       <c r="Q938" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="R938">
         <v>106.59</v>
       </c>
       <c r="S938" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="939" spans="1:19">
@@ -67101,16 +67104,16 @@
         <v>67868</v>
       </c>
       <c r="B939" t="s">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="C939" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="D939" t="s">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="E939" t="s">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="F939" t="s">
         <v>585</v>
@@ -67146,7 +67149,7 @@
         <v>4.7</v>
       </c>
       <c r="Q939" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="R939">
         <v>108.75</v>
@@ -67160,10 +67163,10 @@
         <v>67869</v>
       </c>
       <c r="B940" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="C940" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="D940" t="s">
         <v>682</v>
@@ -67205,7 +67208,7 @@
         <v>15.2</v>
       </c>
       <c r="Q940" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="R940">
         <v>205.2</v>
@@ -67219,16 +67222,16 @@
         <v>67870</v>
       </c>
       <c r="B941" t="s">
-        <v>3359</v>
+        <v>3360</v>
       </c>
       <c r="C941" t="s">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="D941" t="s">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="E941" t="s">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="F941" t="s">
         <v>570</v>
@@ -67264,7 +67267,7 @@
         <v>23.84</v>
       </c>
       <c r="Q941" t="s">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="R941">
         <v>367.2</v>
@@ -67278,16 +67281,16 @@
         <v>67871</v>
       </c>
       <c r="B942" t="s">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="C942" t="s">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="D942" t="s">
         <v>31</v>
       </c>
       <c r="E942" t="s">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="F942" t="s">
         <v>270</v>
@@ -67323,7 +67326,7 @@
         <v>34.11</v>
       </c>
       <c r="Q942" t="s">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="R942">
         <v>516.57</v>
@@ -67337,16 +67340,16 @@
         <v>67872</v>
       </c>
       <c r="B943" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="C943" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="D943" t="s">
         <v>1416</v>
       </c>
       <c r="E943" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="F943" t="s">
         <v>424</v>
@@ -67382,7 +67385,7 @@
         <v>36.45</v>
       </c>
       <c r="Q943" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="R943">
         <v>548.16</v>
@@ -67396,10 +67399,10 @@
         <v>67873</v>
       </c>
       <c r="B944" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="C944" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="D944" t="s">
         <v>2943</v>
@@ -67441,7 +67444,7 @@
         <v>19.04</v>
       </c>
       <c r="Q944" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="R944">
         <v>324.0</v>
@@ -67455,16 +67458,16 @@
         <v>67874</v>
       </c>
       <c r="B945" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="C945" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="D945" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="E945" t="s">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="F945" t="s">
         <v>172</v>
@@ -67500,7 +67503,7 @@
         <v>35.6</v>
       </c>
       <c r="Q945" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="R945">
         <v>525.88</v>
@@ -67514,10 +67517,10 @@
         <v>67875</v>
       </c>
       <c r="B946" t="s">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="C946" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="D946" t="s">
         <v>176</v>
@@ -67559,7 +67562,7 @@
         <v>12.0</v>
       </c>
       <c r="Q946" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="R946">
         <v>162.0</v>
@@ -67573,16 +67576,16 @@
         <v>67876</v>
       </c>
       <c r="B947" t="s">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="C947" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="D947" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="E947" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="F947" t="s">
         <v>590</v>
@@ -67618,7 +67621,7 @@
         <v>42.45</v>
       </c>
       <c r="Q947" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="R947">
         <v>639.98</v>
@@ -67632,16 +67635,16 @@
         <v>67877</v>
       </c>
       <c r="B948" t="s">
+        <v>3382</v>
+      </c>
+      <c r="C948" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D948" t="s">
+        <v>3380</v>
+      </c>
+      <c r="E948" t="s">
         <v>3381</v>
-      </c>
-      <c r="C948" t="s">
-        <v>3382</v>
-      </c>
-      <c r="D948" t="s">
-        <v>3379</v>
-      </c>
-      <c r="E948" t="s">
-        <v>3380</v>
       </c>
       <c r="F948" t="s">
         <v>462</v>
@@ -67677,7 +67680,7 @@
         <v>42.45</v>
       </c>
       <c r="Q948" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="R948">
         <v>639.98</v>
@@ -67691,16 +67694,16 @@
         <v>67878</v>
       </c>
       <c r="B949" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="C949" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="D949" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="E949" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="F949" t="s">
         <v>468</v>
@@ -67736,7 +67739,7 @@
         <v>19.52</v>
       </c>
       <c r="Q949" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="R949">
         <v>330.63</v>
@@ -67750,16 +67753,16 @@
         <v>67879</v>
       </c>
       <c r="B950" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="C950" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="D950" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="E950" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="F950" t="s">
         <v>595</v>
@@ -67795,7 +67798,7 @@
         <v>33.48</v>
       </c>
       <c r="Q950" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="R950">
         <v>451.94</v>
@@ -67809,16 +67812,16 @@
         <v>67880</v>
       </c>
       <c r="B951" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="C951" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="D951" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="E951" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="F951" t="s">
         <v>600</v>
@@ -67854,7 +67857,7 @@
         <v>42.45</v>
       </c>
       <c r="Q951" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="R951">
         <v>639.98</v>
@@ -67868,10 +67871,10 @@
         <v>67881</v>
       </c>
       <c r="B952" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="C952" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="D952" t="s">
         <v>325</v>
@@ -67913,7 +67916,7 @@
         <v>40.36</v>
       </c>
       <c r="Q952" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="R952">
         <v>590.07</v>
@@ -67927,10 +67930,10 @@
         <v>67882</v>
       </c>
       <c r="B953" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="C953" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="D953" t="s">
         <v>2452</v>
@@ -67972,7 +67975,7 @@
         <v>4.31</v>
       </c>
       <c r="Q953" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="R953">
         <v>103.57</v>
@@ -67986,10 +67989,10 @@
         <v>67883</v>
       </c>
       <c r="B954" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="C954" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="D954" t="s">
         <v>427</v>
@@ -68031,7 +68034,7 @@
         <v>21.44</v>
       </c>
       <c r="Q954" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="R954">
         <v>334.8</v>
@@ -68045,16 +68048,16 @@
         <v>67884</v>
       </c>
       <c r="B955" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="C955" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="D955" t="s">
         <v>244</v>
       </c>
       <c r="E955" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="F955" t="s">
         <v>468</v>
@@ -68090,7 +68093,7 @@
         <v>48.38</v>
       </c>
       <c r="Q955" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="R955">
         <v>719.93</v>
@@ -68104,16 +68107,16 @@
         <v>67885</v>
       </c>
       <c r="B956" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="C956" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="D956" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="E956" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="F956" t="s">
         <v>473</v>
@@ -68149,7 +68152,7 @@
         <v>13.07</v>
       </c>
       <c r="Q956" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="R956">
         <v>221.71</v>
@@ -68163,16 +68166,16 @@
         <v>67886</v>
       </c>
       <c r="B957" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="C957" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="D957" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="E957" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="F957" t="s">
         <v>434</v>
@@ -68208,7 +68211,7 @@
         <v>11.65</v>
       </c>
       <c r="Q957" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="R957">
         <v>200.52</v>
@@ -68222,16 +68225,16 @@
         <v>67887</v>
       </c>
       <c r="B958" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="C958" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="D958" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="E958" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="F958" t="s">
         <v>376</v>
@@ -68267,7 +68270,7 @@
         <v>16.39</v>
       </c>
       <c r="Q958" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="R958">
         <v>266.51</v>
@@ -68281,16 +68284,16 @@
         <v>67888</v>
       </c>
       <c r="B959" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="C959" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="D959" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="E959" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="F959" t="s">
         <v>210</v>
@@ -68326,7 +68329,7 @@
         <v>46.83</v>
       </c>
       <c r="Q959" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="R959">
         <v>677.51</v>
@@ -68340,16 +68343,16 @@
         <v>67889</v>
       </c>
       <c r="B960" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="C960" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="D960" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="E960" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="F960" t="s">
         <v>439</v>
@@ -68385,7 +68388,7 @@
         <v>35.84</v>
       </c>
       <c r="Q960" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="R960">
         <v>539.84</v>
@@ -68399,10 +68402,10 @@
         <v>67890</v>
       </c>
       <c r="B961" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="C961" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="D961" t="s">
         <v>427</v>
@@ -68444,7 +68447,7 @@
         <v>10.24</v>
       </c>
       <c r="Q961" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="R961">
         <v>183.6</v>
@@ -68458,16 +68461,16 @@
         <v>67891</v>
       </c>
       <c r="B962" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="C962" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="D962" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="E962" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="F962" t="s">
         <v>166</v>
@@ -68503,7 +68506,7 @@
         <v>47.12</v>
       </c>
       <c r="Q962" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="R962">
         <v>681.38</v>
@@ -68517,16 +68520,16 @@
         <v>67892</v>
       </c>
       <c r="B963" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="C963" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="D963" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="E963" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="F963" t="s">
         <v>693</v>
@@ -68562,7 +68565,7 @@
         <v>12.95</v>
       </c>
       <c r="Q963" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="R963">
         <v>212.43</v>
@@ -68576,16 +68579,16 @@
         <v>67893</v>
       </c>
       <c r="B964" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="C964" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="D964" t="s">
         <v>2357</v>
       </c>
       <c r="E964" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="F964" t="s">
         <v>684</v>
@@ -68621,7 +68624,7 @@
         <v>13.76</v>
       </c>
       <c r="Q964" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="R964">
         <v>231.12</v>
@@ -68635,16 +68638,16 @@
         <v>67894</v>
       </c>
       <c r="B965" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="C965" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="D965" t="s">
         <v>588</v>
       </c>
       <c r="E965" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="F965" t="s">
         <v>659</v>
@@ -68680,7 +68683,7 @@
         <v>26.77</v>
       </c>
       <c r="Q965" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="R965">
         <v>399.06</v>
@@ -68694,16 +68697,16 @@
         <v>67895</v>
       </c>
       <c r="B966" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="C966" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="D966" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="E966" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="F966" t="s">
         <v>397</v>
@@ -68739,7 +68742,7 @@
         <v>11.28</v>
       </c>
       <c r="Q966" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="R966">
         <v>198.32</v>
@@ -68753,10 +68756,10 @@
         <v>67896</v>
       </c>
       <c r="B967" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="C967" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="D967" t="s">
         <v>2862</v>
@@ -68798,7 +68801,7 @@
         <v>11.84</v>
       </c>
       <c r="Q967" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="R967">
         <v>205.14</v>
@@ -68812,10 +68815,10 @@
         <v>67897</v>
       </c>
       <c r="B968" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="C968" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="D968" t="s">
         <v>2537</v>
@@ -68857,7 +68860,7 @@
         <v>27.94</v>
       </c>
       <c r="Q968" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="R968">
         <v>422.42</v>
@@ -68871,16 +68874,16 @@
         <v>67898</v>
       </c>
       <c r="B969" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C969" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="D969" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="E969" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="F969" t="s">
         <v>546</v>
@@ -68916,7 +68919,7 @@
         <v>15.41</v>
       </c>
       <c r="Q969" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="R969">
         <v>253.25</v>
@@ -68930,10 +68933,10 @@
         <v>67899</v>
       </c>
       <c r="B970" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="C970" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="D970" t="s">
         <v>2737</v>
@@ -68975,7 +68978,7 @@
         <v>13.84</v>
       </c>
       <c r="Q970" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="R970">
         <v>232.09</v>
@@ -68989,16 +68992,16 @@
         <v>67900</v>
       </c>
       <c r="B971" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="C971" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="D971" t="s">
         <v>341</v>
       </c>
       <c r="E971" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="F971" t="s">
         <v>616</v>
@@ -69034,7 +69037,7 @@
         <v>15.58</v>
       </c>
       <c r="Q971" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="R971">
         <v>243.96</v>
@@ -69048,10 +69051,10 @@
         <v>67901</v>
       </c>
       <c r="B972" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="C972" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="D972" t="s">
         <v>3216</v>
@@ -69093,7 +69096,7 @@
         <v>15.2</v>
       </c>
       <c r="Q972" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="R972">
         <v>205.2</v>
@@ -69107,10 +69110,10 @@
         <v>67902</v>
       </c>
       <c r="B973" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="C973" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="D973" t="s">
         <v>3227</v>
@@ -69152,7 +69155,7 @@
         <v>15.08</v>
       </c>
       <c r="Q973" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="R973">
         <v>248.83</v>
@@ -69166,16 +69169,16 @@
         <v>67903</v>
       </c>
       <c r="B974" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="C974" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="D974" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="E974" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="F974" t="s">
         <v>478</v>
@@ -69211,7 +69214,7 @@
         <v>15.04</v>
       </c>
       <c r="Q974" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="R974">
         <v>248.34</v>
@@ -69225,16 +69228,16 @@
         <v>67904</v>
       </c>
       <c r="B975" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="C975" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="D975" t="s">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="E975" t="s">
-        <v>3468</v>
+        <v>3469</v>
       </c>
       <c r="F975" t="s">
         <v>642</v>
@@ -69270,7 +69273,7 @@
         <v>27.92</v>
       </c>
       <c r="Q975" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="R975">
         <v>422.96</v>
@@ -69284,16 +69287,16 @@
         <v>67905</v>
       </c>
       <c r="B976" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="C976" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="D976" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="E976" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="F976" t="s">
         <v>580</v>
@@ -69329,7 +69332,7 @@
         <v>14.63</v>
       </c>
       <c r="Q976" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="R976">
         <v>261.43</v>
@@ -69343,16 +69346,16 @@
         <v>67906</v>
       </c>
       <c r="B977" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="C977" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="D977" t="s">
         <v>682</v>
       </c>
       <c r="E977" t="s">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="F977" t="s">
         <v>349</v>
@@ -69388,7 +69391,7 @@
         <v>22.21</v>
       </c>
       <c r="Q977" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="R977">
         <v>345.11</v>
@@ -69402,16 +69405,16 @@
         <v>67907</v>
       </c>
       <c r="B978" t="s">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="C978" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="D978" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="E978" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="F978" t="s">
         <v>343</v>
@@ -69447,7 +69450,7 @@
         <v>12.53</v>
       </c>
       <c r="Q978" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="R978">
         <v>214.37</v>
@@ -69461,16 +69464,16 @@
         <v>67908</v>
       </c>
       <c r="B979" t="s">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="C979" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="D979" t="s">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="E979" t="s">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="F979" t="s">
         <v>450</v>
@@ -69506,7 +69509,7 @@
         <v>11.36</v>
       </c>
       <c r="Q979" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="R979">
         <v>198.68</v>
@@ -69520,16 +69523,16 @@
         <v>67909</v>
       </c>
       <c r="B980" t="s">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="C980" t="s">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="D980" t="s">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="E980" t="s">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="F980" t="s">
         <v>338</v>
@@ -69565,13 +69568,13 @@
         <v>12.53</v>
       </c>
       <c r="Q980" t="s">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="R980">
         <v>214.37</v>
       </c>
       <c r="S980" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="981" spans="1:19">
@@ -69579,16 +69582,16 @@
         <v>67910</v>
       </c>
       <c r="B981" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="C981" t="s">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="D981" t="s">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="E981" t="s">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="F981" t="s">
         <v>354</v>
@@ -69624,7 +69627,7 @@
         <v>19.93</v>
       </c>
       <c r="Q981" t="s">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="R981">
         <v>314.29</v>
@@ -69638,16 +69641,16 @@
         <v>67911</v>
       </c>
       <c r="B982" t="s">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="C982" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="D982" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="E982" t="s">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="F982" t="s">
         <v>566</v>
@@ -69683,7 +69686,7 @@
         <v>24.56</v>
       </c>
       <c r="Q982" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="R982">
         <v>376.86</v>
@@ -69697,16 +69700,16 @@
         <v>67912</v>
       </c>
       <c r="B983" t="s">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="C983" t="s">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="D983" t="s">
         <v>1329</v>
       </c>
       <c r="E983" t="s">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="F983" t="s">
         <v>333</v>
@@ -69742,13 +69745,13 @@
         <v>20.67</v>
       </c>
       <c r="Q983" t="s">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="R983">
         <v>324.33</v>
       </c>
       <c r="S983" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="984" spans="1:19">
@@ -69756,10 +69759,10 @@
         <v>67913</v>
       </c>
       <c r="B984" t="s">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="C984" t="s">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="D984" t="s">
         <v>2376</v>
@@ -69801,7 +69804,7 @@
         <v>20.67</v>
       </c>
       <c r="Q984" t="s">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="R984">
         <v>324.33</v>
@@ -69815,16 +69818,16 @@
         <v>67914</v>
       </c>
       <c r="B985" t="s">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="C985" t="s">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="D985" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="E985" t="s">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="F985" t="s">
         <v>551</v>
@@ -69860,13 +69863,13 @@
         <v>27.08</v>
       </c>
       <c r="Q985" t="s">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="R985">
         <v>410.86</v>
       </c>
       <c r="S985" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="986" spans="1:19">
@@ -69874,16 +69877,16 @@
         <v>67915</v>
       </c>
       <c r="B986" t="s">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="C986" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="D986" t="s">
         <v>1194</v>
       </c>
       <c r="E986" t="s">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="F986" t="s">
         <v>457</v>
@@ -69919,7 +69922,7 @@
         <v>11.9</v>
       </c>
       <c r="Q986" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="R986">
         <v>205.91</v>
@@ -69933,16 +69936,16 @@
         <v>67916</v>
       </c>
       <c r="B987" t="s">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="C987" t="s">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="D987" t="s">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="E987" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="F987" t="s">
         <v>359</v>
@@ -69978,7 +69981,7 @@
         <v>10.96</v>
       </c>
       <c r="Q987" t="s">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="R987">
         <v>193.26</v>
@@ -69992,7 +69995,7 @@
         <v>67917</v>
       </c>
       <c r="B988" t="s">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="C988" t="s">
         <v>1112</v>
@@ -70001,7 +70004,7 @@
         <v>325</v>
       </c>
       <c r="E988" t="s">
-        <v>3515</v>
+        <v>3516</v>
       </c>
       <c r="F988" t="s">
         <v>488</v>
@@ -70051,7 +70054,7 @@
         <v>67918</v>
       </c>
       <c r="B989" t="s">
-        <v>3516</v>
+        <v>3517</v>
       </c>
       <c r="C989" t="s">
         <v>924</v>
@@ -70060,7 +70063,7 @@
         <v>325</v>
       </c>
       <c r="E989" t="s">
-        <v>3517</v>
+        <v>3518</v>
       </c>
       <c r="F989" t="s">
         <v>499</v>
@@ -70110,16 +70113,16 @@
         <v>67919</v>
       </c>
       <c r="B990" t="s">
-        <v>3518</v>
+        <v>3519</v>
       </c>
       <c r="C990" t="s">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="D990" t="s">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="E990" t="s">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="F990" t="s">
         <v>580</v>
@@ -70155,7 +70158,7 @@
         <v>25.66</v>
       </c>
       <c r="Q990" t="s">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="R990">
         <v>391.62</v>
@@ -70169,16 +70172,16 @@
         <v>67920</v>
       </c>
       <c r="B991" t="s">
-        <v>3522</v>
+        <v>3523</v>
       </c>
       <c r="C991" t="s">
-        <v>3523</v>
+        <v>3524</v>
       </c>
       <c r="D991" t="s">
         <v>588</v>
       </c>
       <c r="E991" t="s">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="F991" t="s">
         <v>343</v>
@@ -70214,7 +70217,7 @@
         <v>17.76</v>
       </c>
       <c r="Q991" t="s">
-        <v>3523</v>
+        <v>3524</v>
       </c>
       <c r="R991">
         <v>285.02</v>
@@ -70228,16 +70231,16 @@
         <v>67921</v>
       </c>
       <c r="B992" t="s">
-        <v>3525</v>
+        <v>3526</v>
       </c>
       <c r="C992" t="s">
-        <v>3526</v>
+        <v>3527</v>
       </c>
       <c r="D992" t="s">
         <v>1997</v>
       </c>
       <c r="E992" t="s">
-        <v>3527</v>
+        <v>3528</v>
       </c>
       <c r="F992" t="s">
         <v>450</v>
@@ -70273,7 +70276,7 @@
         <v>15.04</v>
       </c>
       <c r="Q992" t="s">
-        <v>3526</v>
+        <v>3527</v>
       </c>
       <c r="R992">
         <v>248.34</v>
@@ -70287,16 +70290,16 @@
         <v>67922</v>
       </c>
       <c r="B993" t="s">
-        <v>3528</v>
+        <v>3529</v>
       </c>
       <c r="C993" t="s">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="D993" t="s">
-        <v>3530</v>
+        <v>3531</v>
       </c>
       <c r="E993" t="s">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="F993" t="s">
         <v>338</v>
@@ -70332,13 +70335,13 @@
         <v>5.79</v>
       </c>
       <c r="Q993" t="s">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="R993">
         <v>129.67</v>
       </c>
       <c r="S993" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="994" spans="1:19">
@@ -70346,16 +70349,16 @@
         <v>67923</v>
       </c>
       <c r="B994" t="s">
-        <v>3532</v>
+        <v>3533</v>
       </c>
       <c r="C994" t="s">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="D994" t="s">
         <v>2339</v>
       </c>
       <c r="E994" t="s">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="F994" t="s">
         <v>444</v>
@@ -70391,7 +70394,7 @@
         <v>8.14</v>
       </c>
       <c r="Q994" t="s">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="R994">
         <v>155.16</v>
@@ -70405,16 +70408,16 @@
         <v>67924</v>
       </c>
       <c r="B995" t="s">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="C995" t="s">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="D995" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="E995" t="s">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="F995" t="s">
         <v>566</v>
@@ -70450,7 +70453,7 @@
         <v>34.2</v>
       </c>
       <c r="Q995" t="s">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="R995">
         <v>526.5</v>
@@ -70464,16 +70467,16 @@
         <v>67925</v>
       </c>
       <c r="B996" t="s">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="C996" t="s">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D996" t="s">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="E996" t="s">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="F996" t="s">
         <v>570</v>
@@ -70509,7 +70512,7 @@
         <v>15.04</v>
       </c>
       <c r="Q996" t="s">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="R996">
         <v>248.34</v>
@@ -70523,16 +70526,16 @@
         <v>67926</v>
       </c>
       <c r="B997" t="s">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="C997" t="s">
-        <v>3543</v>
+        <v>3544</v>
       </c>
       <c r="D997" t="s">
-        <v>3544</v>
+        <v>3545</v>
       </c>
       <c r="E997" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="F997" t="s">
         <v>359</v>
@@ -70568,7 +70571,7 @@
         <v>11.92</v>
       </c>
       <c r="Q997" t="s">
-        <v>3543</v>
+        <v>3544</v>
       </c>
       <c r="R997">
         <v>218.94</v>
@@ -70591,7 +70594,7 @@
         <v>325</v>
       </c>
       <c r="E998" t="s">
-        <v>3515</v>
+        <v>3516</v>
       </c>
       <c r="F998" t="s">
         <v>499</v>
@@ -70641,16 +70644,16 @@
         <v>67928</v>
       </c>
       <c r="B999" t="s">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="C999" t="s">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="D999" t="s">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="E999" t="s">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="F999" t="s">
         <v>504</v>
@@ -70686,7 +70689,7 @@
         <v>12.0</v>
       </c>
       <c r="Q999" t="s">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="R999">
         <v>162.0</v>
@@ -70700,16 +70703,16 @@
         <v>67929</v>
       </c>
       <c r="B1000" t="s">
-        <v>3547</v>
+        <v>3548</v>
       </c>
       <c r="C1000" t="s">
-        <v>3548</v>
+        <v>3549</v>
       </c>
       <c r="D1000" t="s">
-        <v>3549</v>
+        <v>3550</v>
       </c>
       <c r="E1000" t="s">
-        <v>3550</v>
+        <v>3551</v>
       </c>
       <c r="F1000" t="s">
         <v>392</v>
@@ -70745,7 +70748,7 @@
         <v>13.49</v>
       </c>
       <c r="Q1000" t="s">
-        <v>3548</v>
+        <v>3549</v>
       </c>
       <c r="R1000">
         <v>219.76</v>
@@ -70759,16 +70762,16 @@
         <v>67931</v>
       </c>
       <c r="B1001" t="s">
-        <v>3551</v>
+        <v>3552</v>
       </c>
       <c r="C1001" t="s">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="D1001" t="s">
-        <v>3553</v>
+        <v>3554</v>
       </c>
       <c r="E1001" t="s">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="F1001" t="s">
         <v>397</v>
@@ -70804,7 +70807,7 @@
         <v>13.68</v>
       </c>
       <c r="Q1001" t="s">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="R1001">
         <v>229.88</v>
@@ -70818,16 +70821,16 @@
         <v>67932</v>
       </c>
       <c r="B1002" t="s">
-        <v>3554</v>
+        <v>3555</v>
       </c>
       <c r="C1002" t="s">
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="D1002" t="s">
-        <v>3556</v>
+        <v>3557</v>
       </c>
       <c r="E1002" t="s">
-        <v>3557</v>
+        <v>3558</v>
       </c>
       <c r="F1002" t="s">
         <v>664</v>
@@ -70863,7 +70866,7 @@
         <v>12.92</v>
       </c>
       <c r="Q1002" t="s">
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="R1002">
         <v>219.62</v>
@@ -70877,16 +70880,16 @@
         <v>67933</v>
       </c>
       <c r="B1003" t="s">
-        <v>3558</v>
+        <v>3559</v>
       </c>
       <c r="C1003" t="s">
-        <v>3559</v>
+        <v>3560</v>
       </c>
       <c r="D1003" t="s">
-        <v>3560</v>
+        <v>3561</v>
       </c>
       <c r="E1003" t="s">
-        <v>3561</v>
+        <v>3562</v>
       </c>
       <c r="F1003" t="s">
         <v>689</v>
@@ -70922,7 +70925,7 @@
         <v>13.68</v>
       </c>
       <c r="Q1003" t="s">
-        <v>3559</v>
+        <v>3560</v>
       </c>
       <c r="R1003">
         <v>229.88</v>
@@ -70936,16 +70939,16 @@
         <v>67934</v>
       </c>
       <c r="B1004" t="s">
-        <v>3562</v>
+        <v>3563</v>
       </c>
       <c r="C1004" t="s">
-        <v>3563</v>
+        <v>3564</v>
       </c>
       <c r="D1004" t="s">
-        <v>3564</v>
+        <v>3565</v>
       </c>
       <c r="E1004" t="s">
-        <v>3565</v>
+        <v>3566</v>
       </c>
       <c r="F1004" t="s">
         <v>408</v>
@@ -70981,7 +70984,7 @@
         <v>13.68</v>
       </c>
       <c r="Q1004" t="s">
-        <v>3563</v>
+        <v>3564</v>
       </c>
       <c r="R1004">
         <v>229.88</v>
@@ -70995,16 +70998,16 @@
         <v>67935</v>
       </c>
       <c r="B1005" t="s">
-        <v>3566</v>
+        <v>3567</v>
       </c>
       <c r="C1005" t="s">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="D1005" t="s">
         <v>497</v>
       </c>
       <c r="E1005" t="s">
-        <v>3568</v>
+        <v>3569</v>
       </c>
       <c r="F1005" t="s">
         <v>546</v>
@@ -71040,7 +71043,7 @@
         <v>8.14</v>
       </c>
       <c r="Q1005" t="s">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="R1005">
         <v>155.16</v>
@@ -71054,16 +71057,16 @@
         <v>67936</v>
       </c>
       <c r="B1006" t="s">
-        <v>3569</v>
+        <v>3570</v>
       </c>
       <c r="C1006" t="s">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="D1006" t="s">
         <v>588</v>
       </c>
       <c r="E1006" t="s">
-        <v>3571</v>
+        <v>3572</v>
       </c>
       <c r="F1006" t="s">
         <v>270</v>
@@ -71099,7 +71102,7 @@
         <v>21.7</v>
       </c>
       <c r="Q1006" t="s">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="R1006">
         <v>349.02</v>
@@ -71113,16 +71116,16 @@
         <v>67937</v>
       </c>
       <c r="B1007" t="s">
-        <v>3572</v>
+        <v>3573</v>
       </c>
       <c r="C1007" t="s">
-        <v>3573</v>
+        <v>3574</v>
       </c>
       <c r="D1007" t="s">
-        <v>3574</v>
+        <v>3575</v>
       </c>
       <c r="E1007" t="s">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="F1007" t="s">
         <v>424</v>
@@ -71158,7 +71161,7 @@
         <v>20.42</v>
       </c>
       <c r="Q1007" t="s">
-        <v>3573</v>
+        <v>3574</v>
       </c>
       <c r="R1007">
         <v>320.98</v>
@@ -71172,16 +71175,16 @@
         <v>67938</v>
       </c>
       <c r="B1008" t="s">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="C1008" t="s">
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="D1008" t="s">
-        <v>3578</v>
+        <v>3579</v>
       </c>
       <c r="E1008" t="s">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="F1008" t="s">
         <v>280</v>
@@ -71217,7 +71220,7 @@
         <v>29.1</v>
       </c>
       <c r="Q1008" t="s">
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="R1008">
         <v>438.21</v>
@@ -71231,10 +71234,10 @@
         <v>67939</v>
       </c>
       <c r="B1009" t="s">
-        <v>3580</v>
+        <v>3581</v>
       </c>
       <c r="C1009" t="s">
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="D1009" t="s">
         <v>222</v>
@@ -71276,7 +71279,7 @@
         <v>17.03</v>
       </c>
       <c r="Q1009" t="s">
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="R1009">
         <v>229.99</v>
@@ -71290,16 +71293,16 @@
         <v>67940</v>
       </c>
       <c r="B1010" t="s">
-        <v>3582</v>
+        <v>3583</v>
       </c>
       <c r="C1010" t="s">
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="D1010" t="s">
-        <v>3584</v>
+        <v>3585</v>
       </c>
       <c r="E1010" t="s">
-        <v>3585</v>
+        <v>3586</v>
       </c>
       <c r="F1010" t="s">
         <v>590</v>
@@ -71335,7 +71338,7 @@
         <v>25.34</v>
       </c>
       <c r="Q1010" t="s">
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="R1010">
         <v>387.34</v>
@@ -71349,16 +71352,16 @@
         <v>67941</v>
       </c>
       <c r="B1011" t="s">
-        <v>3586</v>
+        <v>3587</v>
       </c>
       <c r="C1011" t="s">
-        <v>3587</v>
+        <v>3588</v>
       </c>
       <c r="D1011" t="s">
-        <v>3588</v>
+        <v>3589</v>
       </c>
       <c r="E1011" t="s">
-        <v>3589</v>
+        <v>3590</v>
       </c>
       <c r="F1011" t="s">
         <v>462</v>
@@ -71394,7 +71397,7 @@
         <v>25.34</v>
       </c>
       <c r="Q1011" t="s">
-        <v>3587</v>
+        <v>3588</v>
       </c>
       <c r="R1011">
         <v>387.34</v>
@@ -71408,16 +71411,16 @@
         <v>67942</v>
       </c>
       <c r="B1012" t="s">
-        <v>3590</v>
+        <v>3591</v>
       </c>
       <c r="C1012" t="s">
-        <v>3591</v>
+        <v>3592</v>
       </c>
       <c r="D1012" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="E1012" t="s">
-        <v>3592</v>
+        <v>3593</v>
       </c>
       <c r="F1012" t="s">
         <v>600</v>
@@ -71453,7 +71456,7 @@
         <v>22.21</v>
       </c>
       <c r="Q1012" t="s">
-        <v>3591</v>
+        <v>3592</v>
       </c>
       <c r="R1012">
         <v>366.92</v>
@@ -71467,16 +71470,16 @@
         <v>67943</v>
       </c>
       <c r="B1013" t="s">
-        <v>3593</v>
+        <v>3594</v>
       </c>
       <c r="C1013" t="s">
-        <v>3594</v>
+        <v>3595</v>
       </c>
       <c r="D1013" t="s">
-        <v>3595</v>
+        <v>3596</v>
       </c>
       <c r="E1013" t="s">
-        <v>3596</v>
+        <v>3597</v>
       </c>
       <c r="F1013" t="s">
         <v>473</v>
@@ -71512,7 +71515,7 @@
         <v>15.04</v>
       </c>
       <c r="Q1013" t="s">
-        <v>3594</v>
+        <v>3595</v>
       </c>
       <c r="R1013">
         <v>248.34</v>
@@ -71526,16 +71529,16 @@
         <v>67944</v>
       </c>
       <c r="B1014" t="s">
-        <v>3597</v>
+        <v>3598</v>
       </c>
       <c r="C1014" t="s">
-        <v>3598</v>
+        <v>3599</v>
       </c>
       <c r="D1014" t="s">
-        <v>3599</v>
+        <v>3600</v>
       </c>
       <c r="E1014" t="s">
-        <v>3600</v>
+        <v>3601</v>
       </c>
       <c r="F1014" t="s">
         <v>434</v>
@@ -71571,7 +71574,7 @@
         <v>12.0</v>
       </c>
       <c r="Q1014" t="s">
-        <v>3598</v>
+        <v>3599</v>
       </c>
       <c r="R1014">
         <v>162.0</v>
@@ -71585,16 +71588,16 @@
         <v>67946</v>
       </c>
       <c r="B1015" t="s">
-        <v>3601</v>
+        <v>3602</v>
       </c>
       <c r="C1015" t="s">
-        <v>3602</v>
+        <v>3603</v>
       </c>
       <c r="D1015" t="s">
-        <v>3603</v>
+        <v>3604</v>
       </c>
       <c r="E1015" t="s">
-        <v>3604</v>
+        <v>3605</v>
       </c>
       <c r="F1015" t="s">
         <v>376</v>
@@ -71630,7 +71633,7 @@
         <v>21.97</v>
       </c>
       <c r="Q1015" t="s">
-        <v>3602</v>
+        <v>3603</v>
       </c>
       <c r="R1015">
         <v>352.68</v>
@@ -71644,13 +71647,13 @@
         <v>67947</v>
       </c>
       <c r="B1016" t="s">
-        <v>3605</v>
+        <v>3606</v>
       </c>
       <c r="C1016" t="s">
-        <v>3606</v>
+        <v>3607</v>
       </c>
       <c r="D1016" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="E1016" t="s">
         <v>1187</v>
@@ -71689,7 +71692,7 @@
         <v>21.26</v>
       </c>
       <c r="Q1016" t="s">
-        <v>3606</v>
+        <v>3607</v>
       </c>
       <c r="R1016">
         <v>343.04</v>
@@ -71703,16 +71706,16 @@
         <v>67948</v>
       </c>
       <c r="B1017" t="s">
-        <v>3607</v>
+        <v>3608</v>
       </c>
       <c r="C1017" t="s">
-        <v>3608</v>
+        <v>3609</v>
       </c>
       <c r="D1017" t="s">
         <v>1627</v>
       </c>
       <c r="E1017" t="s">
-        <v>3609</v>
+        <v>3610</v>
       </c>
       <c r="F1017" t="s">
         <v>198</v>
@@ -71748,7 +71751,7 @@
         <v>21.7</v>
       </c>
       <c r="Q1017" t="s">
-        <v>3608</v>
+        <v>3609</v>
       </c>
       <c r="R1017">
         <v>349.02</v>
@@ -71762,10 +71765,10 @@
         <v>67949</v>
       </c>
       <c r="B1018" t="s">
-        <v>3610</v>
+        <v>3611</v>
       </c>
       <c r="C1018" t="s">
-        <v>3611</v>
+        <v>3612</v>
       </c>
       <c r="D1018" t="s">
         <v>2409</v>
@@ -71807,7 +71810,7 @@
         <v>14.21</v>
       </c>
       <c r="Q1018" t="s">
-        <v>3611</v>
+        <v>3612</v>
       </c>
       <c r="R1018">
         <v>237.06</v>
@@ -71821,13 +71824,13 @@
         <v>67950</v>
       </c>
       <c r="B1019" t="s">
-        <v>3612</v>
+        <v>3613</v>
       </c>
       <c r="C1019" t="s">
-        <v>3613</v>
+        <v>3614</v>
       </c>
       <c r="D1019" t="s">
-        <v>3614</v>
+        <v>3615</v>
       </c>
       <c r="E1019" t="s">
         <v>341</v>
@@ -71866,7 +71869,7 @@
         <v>15.04</v>
       </c>
       <c r="Q1019" t="s">
-        <v>3613</v>
+        <v>3614</v>
       </c>
       <c r="R1019">
         <v>248.34</v>
@@ -71880,13 +71883,13 @@
         <v>67951</v>
       </c>
       <c r="B1020" t="s">
-        <v>3615</v>
+        <v>3616</v>
       </c>
       <c r="C1020" t="s">
-        <v>3616</v>
+        <v>3617</v>
       </c>
       <c r="D1020" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="E1020" t="s">
         <v>1997</v>
@@ -71925,7 +71928,7 @@
         <v>15.04</v>
       </c>
       <c r="Q1020" t="s">
-        <v>3616</v>
+        <v>3617</v>
       </c>
       <c r="R1020">
         <v>248.34</v>
@@ -71939,16 +71942,16 @@
         <v>67952</v>
       </c>
       <c r="B1021" t="s">
-        <v>3617</v>
+        <v>3618</v>
       </c>
       <c r="C1021" t="s">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="D1021" t="s">
-        <v>3619</v>
+        <v>3620</v>
       </c>
       <c r="E1021" t="s">
-        <v>3620</v>
+        <v>3621</v>
       </c>
       <c r="F1021" t="s">
         <v>303</v>
@@ -71984,7 +71987,7 @@
         <v>15.04</v>
       </c>
       <c r="Q1021" t="s">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="R1021">
         <v>248.34</v>
@@ -71998,10 +72001,10 @@
         <v>67990</v>
       </c>
       <c r="B1022" t="s">
-        <v>3621</v>
+        <v>3622</v>
       </c>
       <c r="C1022" t="s">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="D1022" t="s">
         <v>1588</v>
@@ -72043,7 +72046,7 @@
         <v>11.6</v>
       </c>
       <c r="Q1022" t="s">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="R1022">
         <v>156.6</v>
@@ -72060,13 +72063,13 @@
         <v>2256</v>
       </c>
       <c r="C1023" t="s">
-        <v>3623</v>
+        <v>3624</v>
       </c>
       <c r="D1023" t="s">
         <v>1997</v>
       </c>
       <c r="E1023" t="s">
-        <v>3624</v>
+        <v>3625</v>
       </c>
       <c r="F1023" t="s">
         <v>504</v>
@@ -72102,7 +72105,7 @@
         <v>4.3</v>
       </c>
       <c r="Q1023" t="s">
-        <v>3623</v>
+        <v>3624</v>
       </c>
       <c r="R1023">
         <v>103.29</v>
@@ -72125,7 +72128,7 @@
         <v>2327</v>
       </c>
       <c r="E1024" t="s">
-        <v>3625</v>
+        <v>3626</v>
       </c>
       <c r="F1024" t="s">
         <v>488</v>
@@ -72175,16 +72178,16 @@
         <v>67993</v>
       </c>
       <c r="B1025" t="s">
-        <v>3626</v>
+        <v>3627</v>
       </c>
       <c r="C1025" t="s">
-        <v>3627</v>
+        <v>3628</v>
       </c>
       <c r="D1025" t="s">
-        <v>3628</v>
+        <v>3629</v>
       </c>
       <c r="E1025" t="s">
-        <v>3629</v>
+        <v>3630</v>
       </c>
       <c r="F1025" t="s">
         <v>580</v>
@@ -72220,7 +72223,7 @@
         <v>27.79</v>
       </c>
       <c r="Q1025" t="s">
-        <v>3627</v>
+        <v>3628</v>
       </c>
       <c r="R1025">
         <v>420.43</v>
@@ -72234,10 +72237,10 @@
         <v>67994</v>
       </c>
       <c r="B1026" t="s">
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="C1026" t="s">
-        <v>3631</v>
+        <v>3632</v>
       </c>
       <c r="D1026" t="s">
         <v>239</v>
@@ -72279,7 +72282,7 @@
         <v>17.6</v>
       </c>
       <c r="Q1026" t="s">
-        <v>3631</v>
+        <v>3632</v>
       </c>
       <c r="R1026">
         <v>237.6</v>
@@ -72293,10 +72296,10 @@
         <v>67995</v>
       </c>
       <c r="B1027" t="s">
-        <v>3632</v>
+        <v>3633</v>
       </c>
       <c r="C1027" t="s">
-        <v>3633</v>
+        <v>3634</v>
       </c>
       <c r="D1027" t="s">
         <v>146</v>
@@ -72338,7 +72341,7 @@
         <v>8.21</v>
       </c>
       <c r="Q1027" t="s">
-        <v>3633</v>
+        <v>3634</v>
       </c>
       <c r="R1027">
         <v>110.87</v>
@@ -72352,16 +72355,16 @@
         <v>67996</v>
       </c>
       <c r="B1028" t="s">
-        <v>3634</v>
+        <v>3635</v>
       </c>
       <c r="C1028" t="s">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="D1028" t="s">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="E1028" t="s">
-        <v>3637</v>
+        <v>3638</v>
       </c>
       <c r="F1028" t="s">
         <v>457</v>
@@ -72397,7 +72400,7 @@
         <v>6.88</v>
       </c>
       <c r="Q1028" t="s">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="R1028">
         <v>145.57</v>
@@ -72417,10 +72420,10 @@
         <v>933</v>
       </c>
       <c r="D1029" t="s">
-        <v>3638</v>
+        <v>3639</v>
       </c>
       <c r="E1029" t="s">
-        <v>3639</v>
+        <v>3640</v>
       </c>
       <c r="F1029" t="s">
         <v>488</v>
@@ -72470,16 +72473,16 @@
         <v>67998</v>
       </c>
       <c r="B1030" t="s">
-        <v>3640</v>
+        <v>3641</v>
       </c>
       <c r="C1030" t="s">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="D1030" t="s">
         <v>2893</v>
       </c>
       <c r="E1030" t="s">
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="F1030" t="s">
         <v>231</v>
@@ -72515,13 +72518,13 @@
         <v>61.73</v>
       </c>
       <c r="Q1030" t="s">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="R1030">
         <v>833.33</v>
       </c>
       <c r="S1030" t="s">
-        <v>3643</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="1031" spans="1:19">
@@ -72529,13 +72532,13 @@
         <v>67999</v>
       </c>
       <c r="B1031" t="s">
-        <v>3644</v>
+        <v>3645</v>
       </c>
       <c r="C1031" t="s">
-        <v>3645</v>
+        <v>3646</v>
       </c>
       <c r="D1031" t="s">
-        <v>3646</v>
+        <v>3647</v>
       </c>
       <c r="E1031" t="s">
         <v>1948</v>
@@ -72574,7 +72577,7 @@
         <v>12.08</v>
       </c>
       <c r="Q1031" t="s">
-        <v>3645</v>
+        <v>3646</v>
       </c>
       <c r="R1031">
         <v>208.28</v>
@@ -72588,16 +72591,16 @@
         <v>68000</v>
       </c>
       <c r="B1032" t="s">
-        <v>3647</v>
+        <v>3648</v>
       </c>
       <c r="C1032" t="s">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="D1032" t="s">
         <v>3126</v>
       </c>
       <c r="E1032" t="s">
-        <v>3649</v>
+        <v>3650</v>
       </c>
       <c r="F1032" t="s">
         <v>343</v>
@@ -72633,7 +72636,7 @@
         <v>8.01</v>
       </c>
       <c r="Q1032" t="s">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="R1032">
         <v>162.02</v>
@@ -72647,16 +72650,16 @@
         <v>68001</v>
       </c>
       <c r="B1033" t="s">
-        <v>3516</v>
+        <v>3517</v>
       </c>
       <c r="C1033" t="s">
-        <v>3650</v>
+        <v>3651</v>
       </c>
       <c r="D1033" t="s">
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="E1033" t="s">
-        <v>3652</v>
+        <v>3653</v>
       </c>
       <c r="F1033" t="s">
         <v>931</v>
@@ -72692,7 +72695,7 @@
         <v>11.84</v>
       </c>
       <c r="Q1033" t="s">
-        <v>3650</v>
+        <v>3651</v>
       </c>
       <c r="R1033">
         <v>205.08</v>
@@ -72709,7 +72712,7 @@
         <v>2262</v>
       </c>
       <c r="C1034" t="s">
-        <v>3653</v>
+        <v>3654</v>
       </c>
       <c r="D1034" t="s">
         <v>3088</v>
@@ -72751,7 +72754,7 @@
         <v>3.98</v>
       </c>
       <c r="Q1034" t="s">
-        <v>3653</v>
+        <v>3654</v>
       </c>
       <c r="R1034">
         <v>99.0</v>
@@ -72765,16 +72768,16 @@
         <v>68003</v>
       </c>
       <c r="B1035" t="s">
-        <v>3654</v>
+        <v>3655</v>
       </c>
       <c r="C1035" t="s">
-        <v>3655</v>
+        <v>3656</v>
       </c>
       <c r="D1035" t="s">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="E1035" t="s">
-        <v>3657</v>
+        <v>3658</v>
       </c>
       <c r="F1035" t="s">
         <v>280</v>
@@ -72810,7 +72813,7 @@
         <v>21.86</v>
       </c>
       <c r="Q1035" t="s">
-        <v>3655</v>
+        <v>3656</v>
       </c>
       <c r="R1035">
         <v>295.22</v>
@@ -72824,16 +72827,16 @@
         <v>68004</v>
       </c>
       <c r="B1036" t="s">
-        <v>3658</v>
+        <v>3659</v>
       </c>
       <c r="C1036" t="s">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="D1036" t="s">
         <v>1194</v>
       </c>
       <c r="E1036" t="s">
-        <v>3660</v>
+        <v>3661</v>
       </c>
       <c r="F1036" t="s">
         <v>674</v>
@@ -72869,13 +72872,13 @@
         <v>11.28</v>
       </c>
       <c r="Q1036" t="s">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="R1036">
         <v>196.33</v>
       </c>
       <c r="S1036" t="s">
-        <v>3289</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="1037" spans="1:19">
@@ -72883,16 +72886,16 @@
         <v>68005</v>
       </c>
       <c r="B1037" t="s">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="C1037" t="s">
-        <v>3661</v>
+        <v>3662</v>
       </c>
       <c r="D1037" t="s">
         <v>888</v>
       </c>
       <c r="E1037" t="s">
-        <v>3662</v>
+        <v>3663</v>
       </c>
       <c r="F1037" t="s">
         <v>403</v>
@@ -72928,7 +72931,7 @@
         <v>18.8</v>
       </c>
       <c r="Q1037" t="s">
-        <v>3661</v>
+        <v>3662</v>
       </c>
       <c r="R1037">
         <v>299.88</v>
@@ -72942,16 +72945,16 @@
         <v>68006</v>
       </c>
       <c r="B1038" t="s">
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="C1038" t="s">
         <v>1160</v>
       </c>
       <c r="D1038" t="s">
-        <v>3664</v>
+        <v>3665</v>
       </c>
       <c r="E1038" t="s">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="F1038" t="s">
         <v>499</v>
@@ -73001,16 +73004,16 @@
         <v>68007</v>
       </c>
       <c r="B1039" t="s">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="C1039" t="s">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="D1039" t="s">
         <v>1759</v>
       </c>
       <c r="E1039" t="s">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="F1039" t="s">
         <v>689</v>
@@ -73046,7 +73049,7 @@
         <v>7.14</v>
       </c>
       <c r="Q1039" t="s">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="R1039">
         <v>141.69</v>
@@ -73060,16 +73063,16 @@
         <v>68008</v>
       </c>
       <c r="B1040" t="s">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="C1040" t="s">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="D1040" t="s">
-        <v>3671</v>
+        <v>3672</v>
       </c>
       <c r="E1040" t="s">
-        <v>3672</v>
+        <v>3673</v>
       </c>
       <c r="F1040" t="s">
         <v>693</v>
@@ -73105,7 +73108,7 @@
         <v>6.74</v>
       </c>
       <c r="Q1040" t="s">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="R1040">
         <v>128.65</v>
@@ -73119,16 +73122,16 @@
         <v>68009</v>
       </c>
       <c r="B1041" t="s">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="C1041" t="s">
-        <v>3674</v>
+        <v>3675</v>
       </c>
       <c r="D1041" t="s">
         <v>776</v>
       </c>
       <c r="E1041" t="s">
-        <v>3675</v>
+        <v>3676</v>
       </c>
       <c r="F1041" t="s">
         <v>493</v>
@@ -73164,7 +73167,7 @@
         <v>21.39</v>
       </c>
       <c r="Q1041" t="s">
-        <v>3674</v>
+        <v>3675</v>
       </c>
       <c r="R1041">
         <v>344.02</v>
@@ -73184,10 +73187,10 @@
         <v>2006</v>
       </c>
       <c r="D1042" t="s">
-        <v>3676</v>
+        <v>3677</v>
       </c>
       <c r="E1042" t="s">
-        <v>3677</v>
+        <v>3678</v>
       </c>
       <c r="F1042" t="s">
         <v>654</v>
@@ -73246,7 +73249,7 @@
         <v>1997</v>
       </c>
       <c r="E1043" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
       <c r="F1043" t="s">
         <v>493</v>
@@ -73296,10 +73299,10 @@
         <v>68012</v>
       </c>
       <c r="B1044" t="s">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="C1044" t="s">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="D1044" t="s">
         <v>146</v>
@@ -73341,7 +73344,7 @@
         <v>8.21</v>
       </c>
       <c r="Q1044" t="s">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="R1044">
         <v>110.87</v>
@@ -73355,7 +73358,7 @@
         <v>68013</v>
       </c>
       <c r="B1045" t="s">
-        <v>3681</v>
+        <v>3682</v>
       </c>
       <c r="C1045" t="s">
         <v>912</v>
@@ -73364,7 +73367,7 @@
         <v>3171</v>
       </c>
       <c r="E1045" t="s">
-        <v>3682</v>
+        <v>3683</v>
       </c>
       <c r="F1045" t="s">
         <v>654</v>
@@ -73417,13 +73420,13 @@
         <v>2258</v>
       </c>
       <c r="C1046" t="s">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="D1046" t="s">
-        <v>3684</v>
+        <v>3685</v>
       </c>
       <c r="E1046" t="s">
-        <v>3685</v>
+        <v>3686</v>
       </c>
       <c r="F1046" t="s">
         <v>523</v>
@@ -73459,7 +73462,7 @@
         <v>13.16</v>
       </c>
       <c r="Q1046" t="s">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="R1046">
         <v>221.66</v>
@@ -73524,7 +73527,7 @@
         <v>280.8</v>
       </c>
       <c r="S1047" t="s">
-        <v>3686</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="1048" spans="1:19">
@@ -73532,10 +73535,10 @@
         <v>68062</v>
       </c>
       <c r="B1048" t="s">
-        <v>3687</v>
+        <v>3688</v>
       </c>
       <c r="C1048" t="s">
-        <v>3688</v>
+        <v>3689</v>
       </c>
       <c r="D1048" t="s">
         <v>2796</v>
@@ -73577,13 +73580,13 @@
         <v>10.87</v>
       </c>
       <c r="Q1048" t="s">
-        <v>3688</v>
+        <v>3689</v>
       </c>
       <c r="R1048">
         <v>191.97</v>
       </c>
       <c r="S1048" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="1049" spans="1:19">
@@ -73591,10 +73594,10 @@
         <v>68063</v>
       </c>
       <c r="B1049" t="s">
-        <v>3689</v>
+        <v>3690</v>
       </c>
       <c r="C1049" t="s">
-        <v>3690</v>
+        <v>3691</v>
       </c>
       <c r="D1049" t="s">
         <v>2796</v>
@@ -73636,13 +73639,13 @@
         <v>10.87</v>
       </c>
       <c r="Q1049" t="s">
-        <v>3690</v>
+        <v>3691</v>
       </c>
       <c r="R1049">
         <v>191.97</v>
       </c>
       <c r="S1049" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="1050" spans="1:19">
@@ -73650,16 +73653,16 @@
         <v>68066</v>
       </c>
       <c r="B1050" t="s">
-        <v>3691</v>
+        <v>3692</v>
       </c>
       <c r="C1050" t="s">
-        <v>3692</v>
+        <v>3693</v>
       </c>
       <c r="D1050" t="s">
-        <v>3693</v>
+        <v>3694</v>
       </c>
       <c r="E1050" t="s">
-        <v>3694</v>
+        <v>3695</v>
       </c>
       <c r="F1050" t="s">
         <v>260</v>
@@ -73695,13 +73698,13 @@
         <v>56.93</v>
       </c>
       <c r="Q1050" t="s">
-        <v>3692</v>
+        <v>3693</v>
       </c>
       <c r="R1050">
         <v>768.62</v>
       </c>
       <c r="S1050" t="s">
-        <v>3695</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="1051" spans="1:19">
@@ -73709,16 +73712,16 @@
         <v>68067</v>
       </c>
       <c r="B1051" t="s">
-        <v>3696</v>
+        <v>3697</v>
       </c>
       <c r="C1051" t="s">
-        <v>3697</v>
+        <v>3698</v>
       </c>
       <c r="D1051" t="s">
         <v>164</v>
       </c>
       <c r="E1051" t="s">
-        <v>3698</v>
+        <v>3699</v>
       </c>
       <c r="F1051" t="s">
         <v>256</v>
@@ -73754,13 +73757,13 @@
         <v>56.93</v>
       </c>
       <c r="Q1051" t="s">
-        <v>3697</v>
+        <v>3698</v>
       </c>
       <c r="R1051">
         <v>768.62</v>
       </c>
       <c r="S1051" t="s">
-        <v>3699</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="1052" spans="1:19">
@@ -73768,16 +73771,16 @@
         <v>68068</v>
       </c>
       <c r="B1052" t="s">
-        <v>3700</v>
+        <v>3701</v>
       </c>
       <c r="C1052" t="s">
-        <v>3701</v>
+        <v>3702</v>
       </c>
       <c r="D1052" t="s">
         <v>249</v>
       </c>
       <c r="E1052" t="s">
-        <v>3702</v>
+        <v>3703</v>
       </c>
       <c r="F1052" t="s">
         <v>251</v>
@@ -73813,13 +73816,13 @@
         <v>56.93</v>
       </c>
       <c r="Q1052" t="s">
-        <v>3701</v>
+        <v>3702</v>
       </c>
       <c r="R1052">
         <v>768.62</v>
       </c>
       <c r="S1052" t="s">
-        <v>3703</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="1053" spans="1:19">
@@ -73827,10 +73830,10 @@
         <v>68069</v>
       </c>
       <c r="B1053" t="s">
-        <v>3704</v>
+        <v>3705</v>
       </c>
       <c r="C1053" t="s">
-        <v>3705</v>
+        <v>3706</v>
       </c>
       <c r="D1053" t="s">
         <v>1075</v>
@@ -73872,7 +73875,7 @@
         <v>17.05</v>
       </c>
       <c r="Q1053" t="s">
-        <v>3705</v>
+        <v>3706</v>
       </c>
       <c r="R1053">
         <v>286.28</v>
@@ -73886,16 +73889,16 @@
         <v>68070</v>
       </c>
       <c r="B1054" t="s">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="C1054" t="s">
-        <v>3707</v>
+        <v>3708</v>
       </c>
       <c r="D1054" t="s">
-        <v>3693</v>
+        <v>3694</v>
       </c>
       <c r="E1054" t="s">
-        <v>3694</v>
+        <v>3695</v>
       </c>
       <c r="F1054" t="s">
         <v>260</v>
@@ -73931,13 +73934,13 @@
         <v>24.4</v>
       </c>
       <c r="Q1054" t="s">
-        <v>3707</v>
+        <v>3708</v>
       </c>
       <c r="R1054">
         <v>329.41</v>
       </c>
       <c r="S1054" t="s">
-        <v>3695</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="1055" spans="1:19">
@@ -73945,16 +73948,16 @@
         <v>68071</v>
       </c>
       <c r="B1055" t="s">
-        <v>3708</v>
+        <v>3709</v>
       </c>
       <c r="C1055" t="s">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="D1055" t="s">
         <v>164</v>
       </c>
       <c r="E1055" t="s">
-        <v>3698</v>
+        <v>3699</v>
       </c>
       <c r="F1055" t="s">
         <v>256</v>
@@ -73990,13 +73993,13 @@
         <v>24.4</v>
       </c>
       <c r="Q1055" t="s">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="R1055">
         <v>329.41</v>
       </c>
       <c r="S1055" t="s">
-        <v>3699</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="1056" spans="1:19">
@@ -74004,16 +74007,16 @@
         <v>68072</v>
       </c>
       <c r="B1056" t="s">
-        <v>3710</v>
+        <v>3711</v>
       </c>
       <c r="C1056" t="s">
-        <v>3711</v>
+        <v>3712</v>
       </c>
       <c r="D1056" t="s">
         <v>249</v>
       </c>
       <c r="E1056" t="s">
-        <v>3702</v>
+        <v>3703</v>
       </c>
       <c r="F1056" t="s">
         <v>251</v>
@@ -74049,13 +74052,13 @@
         <v>24.4</v>
       </c>
       <c r="Q1056" t="s">
-        <v>3711</v>
+        <v>3712</v>
       </c>
       <c r="R1056">
         <v>329.41</v>
       </c>
       <c r="S1056" t="s">
-        <v>3703</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="1057" spans="1:19">
@@ -74063,16 +74066,16 @@
         <v>68079</v>
       </c>
       <c r="B1057" t="s">
-        <v>3712</v>
+        <v>3713</v>
       </c>
       <c r="C1057" t="s">
-        <v>3713</v>
+        <v>3714</v>
       </c>
       <c r="D1057" t="s">
-        <v>3714</v>
+        <v>3715</v>
       </c>
       <c r="E1057" t="s">
-        <v>3715</v>
+        <v>3716</v>
       </c>
       <c r="F1057" t="s">
         <v>284</v>
@@ -74108,13 +74111,13 @@
         <v>81.03</v>
       </c>
       <c r="Q1057" t="s">
-        <v>3713</v>
+        <v>3714</v>
       </c>
       <c r="R1057">
         <v>1149.93</v>
       </c>
       <c r="S1057" t="s">
-        <v>3716</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="1058" spans="1:19">
@@ -74122,10 +74125,10 @@
         <v>68080</v>
       </c>
       <c r="B1058" t="s">
-        <v>3717</v>
+        <v>3718</v>
       </c>
       <c r="C1058" t="s">
-        <v>3718</v>
+        <v>3719</v>
       </c>
       <c r="D1058" t="s">
         <v>146</v>
@@ -74167,13 +74170,13 @@
         <v>8.21</v>
       </c>
       <c r="Q1058" t="s">
-        <v>3718</v>
+        <v>3719</v>
       </c>
       <c r="R1058">
         <v>110.87</v>
       </c>
       <c r="S1058" t="s">
-        <v>3716</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="1059" spans="1:19">
@@ -74181,16 +74184,16 @@
         <v>68091</v>
       </c>
       <c r="B1059" t="s">
-        <v>3719</v>
+        <v>3720</v>
       </c>
       <c r="C1059" t="s">
-        <v>3720</v>
+        <v>3721</v>
       </c>
       <c r="D1059" t="s">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="E1059" t="s">
-        <v>3722</v>
+        <v>3723</v>
       </c>
       <c r="F1059" t="s">
         <v>533</v>
@@ -74226,7 +74229,7 @@
         <v>36.09</v>
       </c>
       <c r="Q1059" t="s">
-        <v>3720</v>
+        <v>3721</v>
       </c>
       <c r="R1059">
         <v>532.43</v>
@@ -74240,10 +74243,10 @@
         <v>68092</v>
       </c>
       <c r="B1060" t="s">
-        <v>3723</v>
+        <v>3724</v>
       </c>
       <c r="C1060" t="s">
-        <v>3724</v>
+        <v>3725</v>
       </c>
       <c r="D1060" t="s">
         <v>953</v>
@@ -74285,7 +74288,7 @@
         <v>19.84</v>
       </c>
       <c r="Q1060" t="s">
-        <v>3724</v>
+        <v>3725</v>
       </c>
       <c r="R1060">
         <v>313.2</v>
@@ -74299,16 +74302,16 @@
         <v>68093</v>
       </c>
       <c r="B1061" t="s">
-        <v>3725</v>
+        <v>3726</v>
       </c>
       <c r="C1061" t="s">
-        <v>3726</v>
+        <v>3727</v>
       </c>
       <c r="D1061" t="s">
-        <v>3727</v>
+        <v>3728</v>
       </c>
       <c r="E1061" t="s">
-        <v>3728</v>
+        <v>3729</v>
       </c>
       <c r="F1061" t="s">
         <v>664</v>
@@ -74344,7 +74347,7 @@
         <v>4.84</v>
       </c>
       <c r="Q1061" t="s">
-        <v>3726</v>
+        <v>3727</v>
       </c>
       <c r="R1061">
         <v>110.56</v>
@@ -74358,7 +74361,7 @@
         <v>68094</v>
       </c>
       <c r="B1062" t="s">
-        <v>3729</v>
+        <v>3730</v>
       </c>
       <c r="C1062" t="s">
         <v>1184</v>
@@ -74367,7 +74370,7 @@
         <v>1194</v>
       </c>
       <c r="E1062" t="s">
-        <v>3730</v>
+        <v>3731</v>
       </c>
       <c r="F1062" t="s">
         <v>488</v>
@@ -74417,16 +74420,16 @@
         <v>68095</v>
       </c>
       <c r="B1063" t="s">
-        <v>3731</v>
+        <v>3732</v>
       </c>
       <c r="C1063" t="s">
-        <v>3732</v>
+        <v>3733</v>
       </c>
       <c r="D1063" t="s">
-        <v>3733</v>
+        <v>3734</v>
       </c>
       <c r="E1063" t="s">
-        <v>3734</v>
+        <v>3735</v>
       </c>
       <c r="F1063" t="s">
         <v>595</v>
@@ -74462,7 +74465,7 @@
         <v>23.93</v>
       </c>
       <c r="Q1063" t="s">
-        <v>3732</v>
+        <v>3733</v>
       </c>
       <c r="R1063">
         <v>368.33</v>
@@ -74479,13 +74482,13 @@
         <v>1196</v>
       </c>
       <c r="C1064" t="s">
-        <v>3735</v>
+        <v>3736</v>
       </c>
       <c r="D1064" t="s">
-        <v>3736</v>
+        <v>3737</v>
       </c>
       <c r="E1064" t="s">
-        <v>3737</v>
+        <v>3738</v>
       </c>
       <c r="F1064" t="s">
         <v>504</v>
@@ -74521,13 +74524,13 @@
         <v>5.27</v>
       </c>
       <c r="Q1064" t="s">
-        <v>3735</v>
+        <v>3736</v>
       </c>
       <c r="R1064">
         <v>108.81</v>
       </c>
       <c r="S1064" t="s">
-        <v>3738</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="1065" spans="1:19">
@@ -74586,7 +74589,7 @@
         <v>268.66</v>
       </c>
       <c r="S1065" t="s">
-        <v>3739</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="1066" spans="1:19">
@@ -74594,16 +74597,16 @@
         <v>68106</v>
       </c>
       <c r="B1066" t="s">
-        <v>3740</v>
+        <v>3741</v>
       </c>
       <c r="C1066" t="s">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="D1066" t="s">
-        <v>3742</v>
+        <v>3743</v>
       </c>
       <c r="E1066" t="s">
-        <v>3743</v>
+        <v>3744</v>
       </c>
       <c r="F1066" t="s">
         <v>307</v>
@@ -74639,7 +74642,7 @@
         <v>69.53</v>
       </c>
       <c r="Q1066" t="s">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="R1066">
         <v>1003.52</v>
@@ -74653,10 +74656,10 @@
         <v>68107</v>
       </c>
       <c r="B1067" t="s">
-        <v>3744</v>
+        <v>3745</v>
       </c>
       <c r="C1067" t="s">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="D1067" t="s">
         <v>279</v>
@@ -74698,13 +74701,13 @@
         <v>13.81</v>
       </c>
       <c r="Q1067" t="s">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="R1067">
         <v>186.48</v>
       </c>
       <c r="S1067" t="s">
-        <v>3746</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="1068" spans="1:19">
@@ -74712,10 +74715,10 @@
         <v>68108</v>
       </c>
       <c r="B1068" t="s">
-        <v>3744</v>
+        <v>3745</v>
       </c>
       <c r="C1068" t="s">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="D1068" t="s">
         <v>279</v>
@@ -74757,13 +74760,13 @@
         <v>13.81</v>
       </c>
       <c r="Q1068" t="s">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="R1068">
         <v>231.84</v>
       </c>
       <c r="S1068" t="s">
-        <v>3747</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="1069" spans="1:19">
@@ -74771,13 +74774,13 @@
         <v>68109</v>
       </c>
       <c r="B1069" t="s">
-        <v>3748</v>
+        <v>3749</v>
       </c>
       <c r="C1069" t="s">
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="D1069" t="s">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="E1069"/>
       <c r="F1069" t="s">
@@ -74814,13 +74817,13 @@
         <v>10.32</v>
       </c>
       <c r="Q1069" t="s">
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="R1069">
         <v>139.32</v>
       </c>
       <c r="S1069" t="s">
-        <v>3751</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="1070" spans="1:19">
@@ -74828,13 +74831,13 @@
         <v>68110</v>
       </c>
       <c r="B1070" t="s">
-        <v>3748</v>
+        <v>3749</v>
       </c>
       <c r="C1070" t="s">
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="D1070" t="s">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="E1070"/>
       <c r="F1070" t="s">
@@ -74871,13 +74874,13 @@
         <v>10.32</v>
       </c>
       <c r="Q1070" t="s">
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="R1070">
         <v>184.68</v>
       </c>
       <c r="S1070" t="s">
-        <v>3752</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="1071" spans="1:19">
@@ -74891,10 +74894,10 @@
         <v>1186</v>
       </c>
       <c r="D1071" t="s">
-        <v>3753</v>
+        <v>3754</v>
       </c>
       <c r="E1071" t="s">
-        <v>3754</v>
+        <v>3755</v>
       </c>
       <c r="F1071" t="s">
         <v>654</v>
@@ -74947,10 +74950,10 @@
         <v>1155</v>
       </c>
       <c r="C1072" t="s">
-        <v>3755</v>
+        <v>3756</v>
       </c>
       <c r="D1072" t="s">
-        <v>3756</v>
+        <v>3757</v>
       </c>
       <c r="E1072" t="s">
         <v>682</v>
@@ -74989,7 +74992,7 @@
         <v>13.72</v>
       </c>
       <c r="Q1072" t="s">
-        <v>3755</v>
+        <v>3756</v>
       </c>
       <c r="R1072">
         <v>220.33</v>
@@ -75004,13 +75007,13 @@
       </c>
       <c r="B1073"/>
       <c r="C1073" t="s">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="D1073" t="s">
         <v>134</v>
       </c>
       <c r="E1073" t="s">
-        <v>3758</v>
+        <v>3759</v>
       </c>
       <c r="F1073" t="s">
         <v>2469</v>
@@ -75046,13 +75049,13 @@
         <v>62.71</v>
       </c>
       <c r="Q1073" t="s">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="R1073">
         <v>846.61</v>
       </c>
       <c r="S1073" t="s">
-        <v>3759</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="1074" spans="1:19">
@@ -75060,19 +75063,19 @@
         <v>68332</v>
       </c>
       <c r="B1074" t="s">
-        <v>3760</v>
+        <v>3761</v>
       </c>
       <c r="C1074" t="s">
-        <v>3761</v>
+        <v>3762</v>
       </c>
       <c r="D1074" t="s">
-        <v>3762</v>
+        <v>3763</v>
       </c>
       <c r="E1074" t="s">
         <v>565</v>
       </c>
       <c r="F1074" t="s">
-        <v>3763</v>
+        <v>3764</v>
       </c>
       <c r="G1074" t="s">
         <v>154</v>
@@ -75105,13 +75108,13 @@
         <v>43.94</v>
       </c>
       <c r="Q1074" t="s">
-        <v>3761</v>
+        <v>3762</v>
       </c>
       <c r="R1074">
         <v>693.47</v>
       </c>
       <c r="S1074" t="s">
-        <v>3764</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="1075" spans="1:19">
@@ -75119,10 +75122,10 @@
         <v>68333</v>
       </c>
       <c r="B1075" t="s">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="C1075" t="s">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="D1075" t="s">
         <v>588</v>
@@ -75164,13 +75167,13 @@
         <v>22.49</v>
       </c>
       <c r="Q1075" t="s">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="R1075">
         <v>372.89</v>
       </c>
       <c r="S1075" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1076" spans="1:19">
@@ -75178,10 +75181,10 @@
         <v>68334</v>
       </c>
       <c r="B1076" t="s">
-        <v>3768</v>
+        <v>3769</v>
       </c>
       <c r="C1076" t="s">
-        <v>3769</v>
+        <v>3770</v>
       </c>
       <c r="D1076" t="s">
         <v>869</v>
@@ -75190,7 +75193,7 @@
         <v>870</v>
       </c>
       <c r="F1076" t="s">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="G1076" t="s">
         <v>199</v>
@@ -75223,13 +75226,13 @@
         <v>14.96</v>
       </c>
       <c r="Q1076" t="s">
-        <v>3769</v>
+        <v>3770</v>
       </c>
       <c r="R1076">
         <v>247.16</v>
       </c>
       <c r="S1076" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1077" spans="1:19">
@@ -75237,16 +75240,16 @@
         <v>68335</v>
       </c>
       <c r="B1077" t="s">
-        <v>3771</v>
+        <v>3772</v>
       </c>
       <c r="C1077" t="s">
-        <v>3772</v>
+        <v>3773</v>
       </c>
       <c r="D1077" t="s">
-        <v>3773</v>
+        <v>3774</v>
       </c>
       <c r="E1077" t="s">
-        <v>3774</v>
+        <v>3775</v>
       </c>
       <c r="F1077" t="s">
         <v>998</v>
@@ -75282,13 +75285,13 @@
         <v>6.77</v>
       </c>
       <c r="Q1077" t="s">
-        <v>3772</v>
+        <v>3773</v>
       </c>
       <c r="R1077">
         <v>143.91</v>
       </c>
       <c r="S1077" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1078" spans="1:19">
@@ -75296,16 +75299,16 @@
         <v>68336</v>
       </c>
       <c r="B1078" t="s">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="C1078" t="s">
-        <v>3776</v>
+        <v>3777</v>
       </c>
       <c r="D1078" t="s">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="E1078" t="s">
-        <v>3778</v>
+        <v>3779</v>
       </c>
       <c r="F1078" t="s">
         <v>1827</v>
@@ -75341,13 +75344,13 @@
         <v>109.95</v>
       </c>
       <c r="Q1078" t="s">
-        <v>3776</v>
+        <v>3777</v>
       </c>
       <c r="R1078">
         <v>1529.6</v>
       </c>
       <c r="S1078" t="s">
-        <v>3779</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="1079" spans="1:19">
@@ -75355,16 +75358,16 @@
         <v>68337</v>
       </c>
       <c r="B1079" t="s">
-        <v>3780</v>
+        <v>3781</v>
       </c>
       <c r="C1079" t="s">
-        <v>3781</v>
+        <v>3782</v>
       </c>
       <c r="D1079" t="s">
-        <v>3782</v>
+        <v>3783</v>
       </c>
       <c r="E1079" t="s">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="F1079" t="s">
         <v>998</v>
@@ -75400,13 +75403,13 @@
         <v>9.16</v>
       </c>
       <c r="Q1079" t="s">
-        <v>3781</v>
+        <v>3782</v>
       </c>
       <c r="R1079">
         <v>178.8</v>
       </c>
       <c r="S1079" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1080" spans="1:19">
@@ -75414,16 +75417,16 @@
         <v>68338</v>
       </c>
       <c r="B1080" t="s">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="C1080" t="s">
-        <v>3785</v>
+        <v>3786</v>
       </c>
       <c r="D1080" t="s">
         <v>588</v>
       </c>
       <c r="E1080" t="s">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="F1080" t="s">
         <v>224</v>
@@ -75459,13 +75462,13 @@
         <v>18.42</v>
       </c>
       <c r="Q1080" t="s">
-        <v>3785</v>
+        <v>3786</v>
       </c>
       <c r="R1080">
         <v>304.76</v>
       </c>
       <c r="S1080" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1081" spans="1:19">
@@ -75473,19 +75476,19 @@
         <v>68339</v>
       </c>
       <c r="B1081" t="s">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="C1081" t="s">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="D1081" t="s">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="E1081" t="s">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="F1081" t="s">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="G1081" t="s">
         <v>2149</v>
@@ -75518,13 +75521,13 @@
         <v>6.33</v>
       </c>
       <c r="Q1081" t="s">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="R1081">
         <v>130.67</v>
       </c>
       <c r="S1081" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1082" spans="1:19">
@@ -75532,19 +75535,19 @@
         <v>68340</v>
       </c>
       <c r="B1082" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="C1082" t="s">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="D1082" t="s">
-        <v>3793</v>
+        <v>3794</v>
       </c>
       <c r="E1082" t="s">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="F1082" t="s">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="G1082" t="s">
         <v>2324</v>
@@ -75577,13 +75580,13 @@
         <v>22.21</v>
       </c>
       <c r="Q1082" t="s">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="R1082">
         <v>366.92</v>
       </c>
       <c r="S1082" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1083" spans="1:19">
@@ -75591,13 +75594,13 @@
         <v>68341</v>
       </c>
       <c r="B1083" t="s">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C1083" t="s">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="D1083" t="s">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="E1083" t="s">
         <v>1997</v>
@@ -75636,13 +75639,13 @@
         <v>9.29</v>
       </c>
       <c r="Q1083" t="s">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="R1083">
         <v>170.65</v>
       </c>
       <c r="S1083" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1084" spans="1:19">
@@ -75650,7 +75653,7 @@
         <v>68346</v>
       </c>
       <c r="B1084" t="s">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C1084" t="s">
         <v>1974</v>
@@ -75659,7 +75662,7 @@
         <v>588</v>
       </c>
       <c r="E1084" t="s">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="F1084" t="s">
         <v>931</v>
@@ -75709,19 +75712,19 @@
         <v>68347</v>
       </c>
       <c r="B1085" t="s">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C1085" t="s">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="D1085" t="s">
-        <v>3762</v>
+        <v>3763</v>
       </c>
       <c r="E1085" t="s">
         <v>565</v>
       </c>
       <c r="F1085" t="s">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="G1085" t="s">
         <v>154</v>
@@ -75754,13 +75757,13 @@
         <v>46.13</v>
       </c>
       <c r="Q1085" t="s">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="R1085">
         <v>725.52</v>
       </c>
       <c r="S1085" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1086" spans="1:19">
@@ -75768,19 +75771,19 @@
         <v>68348</v>
       </c>
       <c r="B1086" t="s">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C1086" t="s">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="D1086" t="s">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="E1086" t="s">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="F1086" t="s">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="G1086" t="s">
         <v>182</v>
@@ -75813,13 +75816,13 @@
         <v>12.0</v>
       </c>
       <c r="Q1086" t="s">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="R1086">
         <v>162.0</v>
       </c>
       <c r="S1086" t="s">
-        <v>3764</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="1087" spans="1:19">
@@ -75827,19 +75830,19 @@
         <v>68349</v>
       </c>
       <c r="B1087" t="s">
-        <v>3808</v>
+        <v>3809</v>
       </c>
       <c r="C1087" t="s">
-        <v>3809</v>
+        <v>3810</v>
       </c>
       <c r="D1087" t="s">
         <v>2327</v>
       </c>
       <c r="E1087" t="s">
-        <v>3810</v>
+        <v>3811</v>
       </c>
       <c r="F1087" t="s">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="G1087" t="s">
         <v>193</v>
@@ -75872,13 +75875,13 @@
         <v>9.44</v>
       </c>
       <c r="Q1087" t="s">
-        <v>3809</v>
+        <v>3810</v>
       </c>
       <c r="R1087">
         <v>172.8</v>
       </c>
       <c r="S1087" t="s">
-        <v>3764</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="1088" spans="1:19">
@@ -75886,16 +75889,16 @@
         <v>68351</v>
       </c>
       <c r="B1088" t="s">
-        <v>3811</v>
+        <v>3812</v>
       </c>
       <c r="C1088" t="s">
-        <v>3812</v>
+        <v>3813</v>
       </c>
       <c r="D1088" t="s">
-        <v>3813</v>
+        <v>3814</v>
       </c>
       <c r="E1088" t="s">
-        <v>3814</v>
+        <v>3815</v>
       </c>
       <c r="F1088" t="s">
         <v>679</v>
@@ -75931,7 +75934,7 @@
         <v>14.86</v>
       </c>
       <c r="Q1088" t="s">
-        <v>3812</v>
+        <v>3813</v>
       </c>
       <c r="R1088">
         <v>245.98</v>
@@ -75945,16 +75948,16 @@
         <v>68360</v>
       </c>
       <c r="B1089" t="s">
-        <v>3815</v>
+        <v>3816</v>
       </c>
       <c r="C1089" t="s">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="D1089" t="s">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="E1089" t="s">
-        <v>3818</v>
+        <v>3819</v>
       </c>
       <c r="F1089" t="s">
         <v>166</v>
@@ -75990,13 +75993,13 @@
         <v>9.44</v>
       </c>
       <c r="Q1089" t="s">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="R1089">
         <v>172.8</v>
       </c>
       <c r="S1089" t="s">
-        <v>3819</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="1090" spans="1:19">
@@ -76004,16 +76007,16 @@
         <v>68363</v>
       </c>
       <c r="B1090" t="s">
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="C1090" t="s">
-        <v>3821</v>
+        <v>3822</v>
       </c>
       <c r="D1090" t="s">
         <v>134</v>
       </c>
       <c r="E1090" t="s">
-        <v>3758</v>
+        <v>3759</v>
       </c>
       <c r="F1090" t="s">
         <v>224</v>
@@ -76049,13 +76052,13 @@
         <v>179.23</v>
       </c>
       <c r="Q1090" t="s">
-        <v>3821</v>
+        <v>3822</v>
       </c>
       <c r="R1090">
         <v>2419.66</v>
       </c>
       <c r="S1090" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1091" spans="1:19">
@@ -76075,7 +76078,7 @@
         <v>203</v>
       </c>
       <c r="F1091" t="s">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="G1091" t="s">
         <v>205</v>
@@ -76114,7 +76117,7 @@
         <v>113.91</v>
       </c>
       <c r="S1091" t="s">
-        <v>3822</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="1092" spans="1:19">
@@ -76134,7 +76137,7 @@
         <v>165</v>
       </c>
       <c r="F1092" t="s">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="G1092" t="s">
         <v>167</v>
@@ -76173,7 +76176,7 @@
         <v>114.19</v>
       </c>
       <c r="S1092" t="s">
-        <v>3823</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="1093" spans="1:19">
@@ -76193,7 +76196,7 @@
         <v>1914</v>
       </c>
       <c r="F1093" t="s">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="G1093" t="s">
         <v>871</v>
@@ -76232,7 +76235,7 @@
         <v>265.54</v>
       </c>
       <c r="S1093" t="s">
-        <v>3824</v>
+        <v>3825</v>
       </c>
     </row>
   </sheetData>
